--- a/output/pdf_financials_xlsx/CHR.xlsx
+++ b/output/pdf_financials_xlsx/CHR.xlsx
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>78.00700000000001</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>92.592</v>
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
@@ -2062,10 +2062,10 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>78.00700000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>92.592</v>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>173.517</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>187.069</v>
+        <v>94.477</v>
       </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -22568,7 +22568,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E209" s="5" t="n">

--- a/output/pdf_financials_xlsx/CHR.xlsx
+++ b/output/pdf_financials_xlsx/CHR.xlsx
@@ -6549,40 +6549,40 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>4.059</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.249</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.186</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.497</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.395</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>85.45699999999999</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>1.725</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>271.307</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>7.896</v>
       </c>
     </row>
     <row r="113">
@@ -11832,7 +11832,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E59" s="5" t="n">
         <v>4.059</v>
       </c>
@@ -14994,7 +14998,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
